--- a/output/pdf_financials_xlsx/MEK.xlsx
+++ b/output/pdf_financials_xlsx/MEK.xlsx
@@ -1695,13 +1695,13 @@
         <v>-0.596992</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.578128</v>
+        <v>-1.578128</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.821338</v>
+        <v>-0.821338</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.988833</v>
+        <v>-2.988833</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.490859</v>
@@ -1884,13 +1884,13 @@
         <v>-0.596992</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.578128</v>
+        <v>-1.578128</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.821338</v>
+        <v>-0.821338</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.988833</v>
+        <v>-2.988833</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.490859</v>
@@ -2077,7 +2077,7 @@
         <v>29.8496</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>60.697231</v>
+        <v>-60.697231</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>99.62776700000001</v>
+        <v>-99.62776700000001</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -6469,31 +6469,31 @@
         <v>0.772944</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.40464</v>
+        <v>1.790924</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.819853</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.957639</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.015754</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.051615</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.261305</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.832135</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.19344</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.481992</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -6501,22 +6501,22 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.043473000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.664878</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.643444</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.643444</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>11.086979</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>11.479869</v>
       </c>
     </row>
     <row r="93">
@@ -11492,7 +11492,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -13232,7 +13236,11 @@
           <t>Reserves (note 8) 11,086,979</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -18926,7 +18934,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -20726,7 +20738,11 @@
           <t>Reserves (note 8) 4,819,853</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -45540,16 +45556,16 @@
         </is>
       </c>
       <c r="G344" s="5" t="n">
-        <v>1.578128</v>
+        <v>-1.578128</v>
       </c>
       <c r="H344" s="5" t="n">
-        <v>0.821338</v>
+        <v>-0.821338</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>2.988833</v>
+        <v>-2.988833</v>
       </c>
       <c r="J344" s="5" t="n">
-        <v>0.490859</v>
+        <v>-0.490859</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MEK.xlsx
+++ b/output/pdf_financials_xlsx/MEK.xlsx
@@ -961,7 +961,7 @@
         <v>0.325327</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.838655</v>
+        <v>0.317463</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0.243352</v>
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.009672999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003015</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008987</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.137671</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.088035</v>
+        <v>0.078362</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.362611</v>
+        <v>-0.365626</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.284669</v>
+        <v>1.293656</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.271906</v>
+        <v>1.409577</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>3.106264</v>
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.088035</v>
+        <v>0.078362</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.362611</v>
+        <v>-0.365626</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.284669</v>
+        <v>1.293656</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.271906</v>
+        <v>1.409577</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>3.106264</v>
@@ -2614,28 +2614,28 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.212721</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.079813</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.400687</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.058637</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.117761</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.061649</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.085546</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.5452979999999999</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2643,22 +2643,22 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.205425</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.489132</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.489132</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.096674</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.1395</v>
       </c>
     </row>
     <row r="35">
@@ -2738,49 +2738,49 @@
         <v>2.150514</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>4.831333</v>
+        <v>5.044054</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.914284</v>
+        <v>2.994097</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.442405</v>
+        <v>1.843092</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.018948</v>
+        <v>1.077585</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.317344</v>
+        <v>0.435105</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.247769</v>
+        <v>1.309418</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.254807</v>
+        <v>1.340353</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.606454</v>
+        <v>1.151752</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.405636</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.768277</v>
+        <v>0.973702</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>1.586375</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.289269</v>
+        <v>0.778401</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.289269</v>
+        <v>0.778401</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.096674</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.1395</v>
       </c>
     </row>
     <row r="37">
@@ -3492,28 +3492,28 @@
         <v>0.08691699999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.272916</v>
+        <v>0.060195</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.117956</v>
+        <v>0.038143</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.447762</v>
+        <v>0.047075</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.112147</v>
+        <v>0.05351</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.7354810000000001</v>
+        <v>0.61772</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.679973</v>
+        <v>0.618324</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.286425</v>
+        <v>0.200879</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.7649899999999999</v>
+        <v>0.219692</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3521,22 +3521,22 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.611592</v>
+        <v>0.406167</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>1.571476</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.504252</v>
+        <v>0.01512</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.504252</v>
+        <v>0.01512</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.512067</v>
+        <v>0.415393</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.81648</v>
+        <v>0.67698</v>
       </c>
     </row>
     <row r="49">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -34234,7 +34234,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -47632,7 +47632,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E364" s="5" t="n">

--- a/output/pdf_financials_xlsx/MEK.xlsx
+++ b/output/pdf_financials_xlsx/MEK.xlsx
@@ -24650,7 +24650,11 @@
           <t>Provision for (recovery of) future income taxes</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -26776,7 +26780,11 @@
           <t>Recovery of future income taxes</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>-0.680862</v>
       </c>
